--- a/UTCUTS/A2_Extra_Inputs/A-Xtra_Projections.xlsx
+++ b/UTCUTS/A2_Extra_Inputs/A-Xtra_Projections.xlsx
@@ -1465,7 +1465,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B03E09D-D06B-46F7-9455-B6F7E330E46A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1664CE9F-9B8A-480B-B93C-2B2026276218}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
